--- a/CO - Splunk Intermediate.xlsx
+++ b/CO - Splunk Intermediate.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38A15E01-EC3A-4655-B7AD-43B64264C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_US_09_03_2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3989A12-D437-46D8-868D-808FC634141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -410,7 +415,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,12 +456,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="11">
@@ -585,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -635,6 +646,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -971,16 +988,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40.85546875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.88671875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -990,7 +1007,7 @@
       <c r="C1" s="22"/>
       <c r="D1" s="23"/>
     </row>
-    <row r="2" spans="1:4" ht="29.25" customHeight="1">
+    <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1000,7 +1017,7 @@
       <c r="C2" s="19"/>
       <c r="D2" s="20"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="9" t="s">
         <v>4</v>
@@ -1012,11 +1029,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36" customHeight="1">
+    <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="24" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1026,8 +1043,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5">
-      <c r="B6" s="11" t="s">
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1037,8 +1054,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5">
-      <c r="B7" s="11" t="s">
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="25" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1048,8 +1065,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32.25">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1059,7 +1076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>20</v>
       </c>
@@ -1070,8 +1087,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="32.25">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="24" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1081,8 +1098,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1092,8 +1109,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="32.25">
-      <c r="B12" s="11" t="s">
+    <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -1103,8 +1120,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="32.25">
-      <c r="B13" s="11" t="s">
+    <row r="13" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1114,8 +1131,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5">
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="25" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -1125,7 +1142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5">
+    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>20</v>
       </c>
@@ -1136,8 +1153,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="32.25">
-      <c r="B16" s="10" t="s">
+    <row r="16" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="6" t="s">
@@ -1147,8 +1164,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="16.5">
-      <c r="B17" s="11" t="s">
+    <row r="17" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="25" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -1158,8 +1175,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="32.25">
-      <c r="B18" s="11" t="s">
+    <row r="18" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B18" s="25" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -1169,8 +1186,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="32.25">
-      <c r="B19" s="11" t="s">
+    <row r="19" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="25" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -1180,8 +1197,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="16.5">
-      <c r="B20" s="11" t="s">
+    <row r="20" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B20" s="25" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -1191,7 +1208,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="16.5">
+    <row r="21" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
@@ -1200,8 +1217,8 @@
       </c>
       <c r="D21" s="7"/>
     </row>
-    <row r="22" spans="2:4" ht="32.25">
-      <c r="B22" s="10" t="s">
+    <row r="22" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B22" s="24" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1209,8 +1226,8 @@
       </c>
       <c r="D22" s="7"/>
     </row>
-    <row r="23" spans="2:4" ht="16.5">
-      <c r="B23" s="11" t="s">
+    <row r="23" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="25" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -1218,8 +1235,8 @@
       </c>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="2:4" ht="16.5">
-      <c r="B24" s="11" t="s">
+    <row r="24" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="25" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -1227,7 +1244,7 @@
       </c>
       <c r="D24" s="7"/>
     </row>
-    <row r="25" spans="2:4" ht="16.5">
+    <row r="25" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
         <v>57</v>
       </c>
@@ -1236,8 +1253,8 @@
       </c>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="2:4" ht="32.25">
-      <c r="B26" s="11" t="s">
+    <row r="26" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B26" s="25" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -1245,7 +1262,7 @@
       </c>
       <c r="D26" s="7"/>
     </row>
-    <row r="27" spans="2:4" ht="16.5">
+    <row r="27" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>60</v>
       </c>
@@ -1254,7 +1271,7 @@
       </c>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="2:4" ht="16.5">
+    <row r="28" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>62</v>
       </c>
@@ -1263,8 +1280,8 @@
       </c>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="2:4" ht="16.5">
-      <c r="B29" s="11" t="s">
+    <row r="29" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="25" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -1272,8 +1289,8 @@
       </c>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="2:4" ht="32.25">
-      <c r="B30" s="11" t="s">
+    <row r="30" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B30" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -1281,7 +1298,7 @@
       </c>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" spans="2:4" ht="32.25">
+    <row r="31" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
         <v>68</v>
       </c>
@@ -1290,84 +1307,84 @@
       </c>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" spans="2:4" ht="32.25">
+    <row r="32" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
     </row>
-    <row r="33" spans="1:4" ht="32.25">
+    <row r="33" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
         <v>71</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
     </row>
-    <row r="34" spans="1:4" ht="48.75">
+    <row r="34" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
     </row>
-    <row r="35" spans="1:4" ht="16.5">
+    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5">
+    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
     </row>
-    <row r="37" spans="1:4" ht="16.5">
+    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" s="10" t="s">
         <v>73</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
     </row>
-    <row r="38" spans="1:4" ht="16.5">
+    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
     </row>
-    <row r="39" spans="1:4" ht="16.5">
+    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
     </row>
-    <row r="40" spans="1:4" ht="16.5">
+    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
         <v>76</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="16.5">
+    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" ht="16.5">
+    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42" s="11" t="s">
         <v>78</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="32.25">
+    <row r="43" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="12" t="s">
         <v>79</v>
@@ -1375,7 +1392,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="45" spans="1:4" ht="18.75">
+    <row r="45" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>80</v>
       </c>
@@ -1397,6 +1414,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AF7E30AC51BE24AB98F695D1F646B0D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="944c3efe05a27205f6f8a21900784054">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ac015f5f-37cf-480b-8f61-9f6dcabe93df" xmlns:ns3="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bdc8c47fb571a171e530ebc6f1b62f9" ns2:_="" ns3:_="">
     <xsd:import namespace="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
@@ -1631,34 +1668,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{889D0D1E-5983-4BD8-861A-9A522ED044AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D83723-B2BE-4A67-8F93-1AED761E3ADF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D83723-B2BE-4A67-8F93-1AED761E3ADF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{889D0D1E-5983-4BD8-861A-9A522ED044AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CO - Splunk Intermediate.xlsx
+++ b/CO - Splunk Intermediate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_US_09_03_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3989A12-D437-46D8-868D-808FC634141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396FA33A-3A5B-434C-9DD3-341D06630551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -629,6 +629,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -647,10 +653,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1001,21 +1007,21 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -1033,7 +1039,7 @@
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1044,7 +1050,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1055,7 +1061,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1066,7 +1072,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1088,7 +1094,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1099,7 +1105,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1110,7 +1116,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="19" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -1121,10 +1127,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -1132,10 +1138,10 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -1146,7 +1152,7 @@
       <c r="B15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -1154,10 +1160,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="27" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -1165,46 +1171,46 @@
       </c>
     </row>
     <row r="17" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="26" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="27" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1218,28 +1224,28 @@
       <c r="D21" s="7"/>
     </row>
     <row r="22" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="26" t="s">
         <v>52</v>
       </c>
       <c r="D22" s="7"/>
     </row>
     <row r="23" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D24" s="7"/>
@@ -1248,13 +1254,13 @@
       <c r="B25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D25" s="7"/>
     </row>
     <row r="26" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="19" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -1266,7 +1272,7 @@
       <c r="B27" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="26" t="s">
         <v>61</v>
       </c>
       <c r="D27" s="7"/>
@@ -1275,25 +1281,25 @@
       <c r="B28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="27" t="s">
         <v>63</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="27" t="s">
         <v>65</v>
       </c>
       <c r="D29" s="7"/>
     </row>
     <row r="30" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="27" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="7"/>
@@ -1302,7 +1308,7 @@
       <c r="B31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="27" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="7"/>
@@ -1414,26 +1420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AF7E30AC51BE24AB98F695D1F646B0D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="944c3efe05a27205f6f8a21900784054">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ac015f5f-37cf-480b-8f61-9f6dcabe93df" xmlns:ns3="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bdc8c47fb571a171e530ebc6f1b62f9" ns2:_="" ns3:_="">
     <xsd:import namespace="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
@@ -1668,10 +1654,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{889D0D1E-5983-4BD8-861A-9A522ED044AD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1688,20 +1705,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{889D0D1E-5983-4BD8-861A-9A522ED044AD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
-    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CO - Splunk Intermediate.xlsx
+++ b/CO - Splunk Intermediate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_US_09_03_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396FA33A-3A5B-434C-9DD3-341D06630551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B707878A-24DF-4777-A500-B10E7864E401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,15 +596,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -613,13 +610,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -633,6 +624,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -653,10 +650,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1007,405 +1001,405 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="18" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="18" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="18" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="18" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="7"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="7"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="7"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="7"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="7"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="7"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="7"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="7"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="7"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" spans="2:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
     </row>
     <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="45" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="16"/>
+      <c r="C45" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1420,6 +1414,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AF7E30AC51BE24AB98F695D1F646B0D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="944c3efe05a27205f6f8a21900784054">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ac015f5f-37cf-480b-8f61-9f6dcabe93df" xmlns:ns3="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bdc8c47fb571a171e530ebc6f1b62f9" ns2:_="" ns3:_="">
     <xsd:import namespace="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
@@ -1654,27 +1668,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac015f5f-37cf-480b-8f61-9f6dcabe93df">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D83723-B2BE-4A67-8F93-1AED761E3ADF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{889D0D1E-5983-4BD8-861A-9A522ED044AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1691,23 +1704,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D83723-B2BE-4A67-8F93-1AED761E3ADF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
-    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C898FD-DFB1-448F-9432-BD9DD563A099}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>